--- a/智能问数系统测试用例.xlsx
+++ b/智能问数系统测试用例.xlsx
@@ -10,7 +10,7 @@
     <sheet name="测试问题集" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">测试问题集!$A$1:$B$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">测试问题集!$A$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>序号</t>
   </si>
@@ -38,24 +38,9 @@
     <t>问题</t>
   </si>
   <si>
-    <t>实体筛选</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>张三的户籍信息是什么</t>
-  </si>
-  <si>
-    <t>王芳的出生日期是什么时候</t>
-  </si>
-  <si>
     <t>2025年土葬的有哪些人</t>
   </si>
   <si>
-    <t>张三的配偶是谁</t>
-  </si>
-  <si>
     <t>江苏省户籍有多少人</t>
   </si>
   <si>
@@ -68,12 +53,6 @@
     <t>各年份的殡葬人数分别是多少</t>
   </si>
   <si>
-    <t>王芳的出生日期和婚姻状况</t>
-  </si>
-  <si>
-    <t>张三的户籍信息和配偶姓名</t>
-  </si>
-  <si>
     <t>查询有户籍登记且有婚姻关系的人员名单</t>
   </si>
   <si>
@@ -86,7 +65,7 @@
     <t>查询户籍在江苏或浙江的人员</t>
   </si>
   <si>
-    <t>查询2025年1月殡葬且户籍在江苏省的人员</t>
+    <t>查询2025年12月殡葬且户籍在江苏省的人员</t>
   </si>
   <si>
     <t>查询已婚且户籍未注销的女性人数</t>
@@ -110,12 +89,6 @@
     <t>未婚人口占总人口的比例是多少</t>
   </si>
   <si>
-    <t>张三的婚姻状况变更历史</t>
-  </si>
-  <si>
-    <t>王芳的结离婚记录有哪些</t>
-  </si>
-  <si>
     <t>2020年到2025年每年结婚的人数</t>
   </si>
   <si>
@@ -132,6 +105,9 @@
   </si>
   <si>
     <t>殡葬总人数是多少，以及土葬和火葬各占多少</t>
+  </si>
+  <si>
+    <t>查询江苏省南京市户籍,性别为男,汉族，没有宗教信仰，出生在1987年到1990年之间的且已婚的人员</t>
   </si>
 </sst>
 </file>
@@ -767,13 +743,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1121,269 +1100,214 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="61.125" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1"/>
+    <col min="2" max="2" width="61.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="391.5" spans="1:4">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="229.5" spans="1:4">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="297" spans="1:4">
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="378" spans="1:4">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" ht="297" spans="1:4">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="351" spans="1:4">
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" ht="310.5" spans="1:2">
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" ht="297" spans="1:2">
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" ht="297" spans="1:2">
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" ht="297" spans="1:2">
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" ht="297" spans="1:2">
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22" ht="378" spans="1:2">
-      <c r="A22">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" ht="297" spans="1:2">
-      <c r="A23">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" ht="27" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" ht="391.5" spans="1:2">
-      <c r="A28">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" ht="135" spans="1:2">
-      <c r="A31">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>33</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B31" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B24" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/智能问数系统测试用例.xlsx
+++ b/智能问数系统测试用例.xlsx
@@ -10,7 +10,7 @@
     <sheet name="测试问题集" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">测试问题集!$A$1:$B$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">测试问题集!$A$1:$B$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1307,7 +1307,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B24" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
